--- a/purchase/재료비_정산보고서.xlsx
+++ b/purchase/재료비_정산보고서.xlsx
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
   <si>
     <r>
       <rPr>
@@ -159,6 +159,46 @@
     <t xml:space="preserve">과제명</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">말벌 자동 마킹 트랩 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상용 트랩 레트로핏 모듈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">팀장</t>
   </si>
   <si>
@@ -486,6 +526,120 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">영수증 하나에 여러 줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배송비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이면 같은 영수증 번호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(R-01 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">를 적음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">.</t>
     </r>
   </si>
@@ -905,6 +1059,573 @@
   </si>
   <si>
     <t xml:space="preserve">형식 참고용 — 합계 제외</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불로양봉원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">네이버페이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">말벌포획기 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">형 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">본체 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유인액 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">병</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">상용 트랩 「야생 말벌 포획기」</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">레트로핏 모듈의 바탕 상용 트랩 — 포획통을 격리함으로 사용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">설계 실측</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">표본 채집</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">R-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">배송비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">위 품목 배송</t>
+  </si>
+  <si>
+    <t xml:space="preserve">배송비 인정 여부 확인 필요</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디바이스마트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">네이버페이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라즈베리파이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27W USB-C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아답터 검은색 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공식 정품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.1V 5A, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">케이블 일체</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제어부 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">190 — Pi 5 + AI HAT+ + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">카메라 전원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">R-02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">영수증에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">외 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">으로만 표시 → 주문 상세 캡처를 세부내역으로 첨부</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라즈베리파이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">액티브 쿨러 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Raspberry Pi Active Cooler</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제어부 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">190 — Pi 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방열 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(AI HAT+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R-02 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">영수증에 품목명 없음 → 주문 상세 캡처로 증빙</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">합계</t>
@@ -2193,7 +2914,7 @@
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2328,6 +3049,12 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="12"/>
       <name val="Noto Sans CJK SC"/>
@@ -2438,10 +3165,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2498,6 +3221,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2510,15 +3237,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2808,7 +3535,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2818,942 +3545,954 @@
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3"/>
       <c r="F2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>46323</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="5" t="n">
         <v>500000</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" s="6" t="n">
         <f aca="false">SUM(H9:H38)</f>
-        <v>0</v>
+        <v>86240</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" s="6" t="n">
         <f aca="false">C4-E4</f>
-        <v>500000</v>
+        <v>413760</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="8" t="str">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="str">
         <f aca="false">IF(E4&gt;C4,"한도 초과 — 줄일 것",IF(E4=0,"아직 구매 없음","정상"))</f>
-        <v>아직 구매 없음</v>
-      </c>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
+        <v>정상</v>
+      </c>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
+      <c r="A5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="11" t="s">
+      <c r="A8" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="E8" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="12" t="n">
         <v>8600</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="12" t="n">
         <f aca="false">F8*G8</f>
         <v>8600</v>
       </c>
-      <c r="I8" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="11" t="s">
+      <c r="I8" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="J8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="K8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="L8" s="10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="n">
+      <c r="M8" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="18" t="str">
+      <c r="B9" s="14" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>54000</v>
+      </c>
+      <c r="H9" s="17" t="n">
         <f aca="false">IF(AND(F9&lt;&gt;"",G9&lt;&gt;""),F9*G9,"")</f>
-        <v/>
-      </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A9,"00")</f>
-        <v>R-01</v>
-      </c>
-      <c r="K9" s="14" t="str">
+        <v>54000</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="13" t="str">
         <f aca="false">"사진 "&amp;A9</f>
         <v>사진 1</v>
       </c>
-      <c r="L9" s="16"/>
+      <c r="L9" s="15" t="s">
+        <v>36</v>
+      </c>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="n">
+    <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18" t="str">
+      <c r="B10" s="14" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>3800</v>
+      </c>
+      <c r="H10" s="17" t="n">
         <f aca="false">IF(AND(F10&lt;&gt;"",G10&lt;&gt;""),F10*G10,"")</f>
-        <v/>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A10,"00")</f>
-        <v>R-02</v>
-      </c>
-      <c r="K10" s="14" t="str">
+        <v>3800</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="13" t="str">
         <f aca="false">"사진 "&amp;A10</f>
         <v>사진 2</v>
       </c>
-      <c r="L10" s="16"/>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="n">
+      <c r="L10" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18" t="str">
+      <c r="B11" s="14" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>18040</v>
+      </c>
+      <c r="H11" s="17" t="n">
         <f aca="false">IF(AND(F11&lt;&gt;"",G11&lt;&gt;""),F11*G11,"")</f>
-        <v/>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A11,"00")</f>
-        <v>R-03</v>
-      </c>
-      <c r="K11" s="14" t="str">
+        <v>18040</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11" s="13" t="str">
         <f aca="false">"사진 "&amp;A11</f>
         <v>사진 3</v>
       </c>
-      <c r="L11" s="16"/>
-      <c r="M11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="n">
+      <c r="L11" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18" t="str">
+      <c r="B12" s="14" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>7700</v>
+      </c>
+      <c r="H12" s="17" t="n">
         <f aca="false">IF(AND(F12&lt;&gt;"",G12&lt;&gt;""),F12*G12,"")</f>
-        <v/>
-      </c>
-      <c r="I12" s="3"/>
-      <c r="J12" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A12,"00")</f>
-        <v>R-04</v>
-      </c>
-      <c r="K12" s="14" t="str">
+        <v>7700</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="K12" s="13" t="str">
         <f aca="false">"사진 "&amp;A12</f>
         <v>사진 4</v>
       </c>
-      <c r="L12" s="16"/>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="n">
+      <c r="L12" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="M12" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18" t="str">
+      <c r="B13" s="14" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>2700</v>
+      </c>
+      <c r="H13" s="17" t="n">
         <f aca="false">IF(AND(F13&lt;&gt;"",G13&lt;&gt;""),F13*G13,"")</f>
-        <v/>
-      </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A13,"00")</f>
-        <v>R-05</v>
-      </c>
-      <c r="K13" s="14" t="str">
+        <v>2700</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="K13" s="13" t="str">
         <f aca="false">"사진 "&amp;A13</f>
         <v>사진 5</v>
       </c>
-      <c r="L13" s="16"/>
-      <c r="M13" s="3"/>
+      <c r="L13" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="n">
+      <c r="A14" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="15"/>
+      <c r="B14" s="14"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18" t="str">
+      <c r="F14" s="15"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="17" t="str">
         <f aca="false">IF(AND(F14&lt;&gt;"",G14&lt;&gt;""),F14*G14,"")</f>
         <v/>
       </c>
       <c r="I14" s="3"/>
-      <c r="J14" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A14,"00")</f>
-        <v>R-06</v>
-      </c>
-      <c r="K14" s="14" t="str">
+      <c r="J14" s="15"/>
+      <c r="K14" s="13" t="str">
         <f aca="false">"사진 "&amp;A14</f>
         <v>사진 6</v>
       </c>
-      <c r="L14" s="16"/>
+      <c r="L14" s="15"/>
       <c r="M14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="n">
+      <c r="A15" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="15"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="18" t="str">
+      <c r="F15" s="15"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="17" t="str">
         <f aca="false">IF(AND(F15&lt;&gt;"",G15&lt;&gt;""),F15*G15,"")</f>
         <v/>
       </c>
       <c r="I15" s="3"/>
-      <c r="J15" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A15,"00")</f>
-        <v>R-07</v>
-      </c>
-      <c r="K15" s="14" t="str">
+      <c r="J15" s="15"/>
+      <c r="K15" s="13" t="str">
         <f aca="false">"사진 "&amp;A15</f>
         <v>사진 7</v>
       </c>
-      <c r="L15" s="16"/>
+      <c r="L15" s="15"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="15"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="18" t="str">
+      <c r="F16" s="15"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="17" t="str">
         <f aca="false">IF(AND(F16&lt;&gt;"",G16&lt;&gt;""),F16*G16,"")</f>
         <v/>
       </c>
       <c r="I16" s="3"/>
-      <c r="J16" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A16,"00")</f>
-        <v>R-08</v>
-      </c>
-      <c r="K16" s="14" t="str">
+      <c r="J16" s="15"/>
+      <c r="K16" s="13" t="str">
         <f aca="false">"사진 "&amp;A16</f>
         <v>사진 8</v>
       </c>
-      <c r="L16" s="16"/>
+      <c r="L16" s="15"/>
       <c r="M16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="15"/>
+      <c r="B17" s="14"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="18" t="str">
+      <c r="F17" s="15"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="17" t="str">
         <f aca="false">IF(AND(F17&lt;&gt;"",G17&lt;&gt;""),F17*G17,"")</f>
         <v/>
       </c>
       <c r="I17" s="3"/>
-      <c r="J17" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A17,"00")</f>
-        <v>R-09</v>
-      </c>
-      <c r="K17" s="14" t="str">
+      <c r="J17" s="15"/>
+      <c r="K17" s="13" t="str">
         <f aca="false">"사진 "&amp;A17</f>
         <v>사진 9</v>
       </c>
-      <c r="L17" s="16"/>
+      <c r="L17" s="15"/>
       <c r="M17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="15"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="18" t="str">
+      <c r="F18" s="15"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="17" t="str">
         <f aca="false">IF(AND(F18&lt;&gt;"",G18&lt;&gt;""),F18*G18,"")</f>
         <v/>
       </c>
       <c r="I18" s="3"/>
-      <c r="J18" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A18,"00")</f>
-        <v>R-10</v>
-      </c>
-      <c r="K18" s="14" t="str">
+      <c r="J18" s="15"/>
+      <c r="K18" s="13" t="str">
         <f aca="false">"사진 "&amp;A18</f>
         <v>사진 10</v>
       </c>
-      <c r="L18" s="16"/>
+      <c r="L18" s="15"/>
       <c r="M18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="15"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="18" t="str">
+      <c r="F19" s="15"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="17" t="str">
         <f aca="false">IF(AND(F19&lt;&gt;"",G19&lt;&gt;""),F19*G19,"")</f>
         <v/>
       </c>
       <c r="I19" s="3"/>
-      <c r="J19" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A19,"00")</f>
-        <v>R-11</v>
-      </c>
-      <c r="K19" s="14" t="str">
+      <c r="J19" s="15"/>
+      <c r="K19" s="13" t="str">
         <f aca="false">"사진 "&amp;A19</f>
         <v>사진 11</v>
       </c>
-      <c r="L19" s="16"/>
+      <c r="L19" s="15"/>
       <c r="M19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="15"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="18" t="str">
+      <c r="F20" s="15"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="17" t="str">
         <f aca="false">IF(AND(F20&lt;&gt;"",G20&lt;&gt;""),F20*G20,"")</f>
         <v/>
       </c>
       <c r="I20" s="3"/>
-      <c r="J20" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A20,"00")</f>
-        <v>R-12</v>
-      </c>
-      <c r="K20" s="14" t="str">
+      <c r="J20" s="15"/>
+      <c r="K20" s="13" t="str">
         <f aca="false">"사진 "&amp;A20</f>
         <v>사진 12</v>
       </c>
-      <c r="L20" s="16"/>
+      <c r="L20" s="15"/>
       <c r="M20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="15"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="18" t="str">
+      <c r="F21" s="15"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="17" t="str">
         <f aca="false">IF(AND(F21&lt;&gt;"",G21&lt;&gt;""),F21*G21,"")</f>
         <v/>
       </c>
       <c r="I21" s="3"/>
-      <c r="J21" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A21,"00")</f>
-        <v>R-13</v>
-      </c>
-      <c r="K21" s="14" t="str">
+      <c r="J21" s="15"/>
+      <c r="K21" s="13" t="str">
         <f aca="false">"사진 "&amp;A21</f>
         <v>사진 13</v>
       </c>
-      <c r="L21" s="16"/>
+      <c r="L21" s="15"/>
       <c r="M21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="15"/>
+      <c r="B22" s="14"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="18" t="str">
+      <c r="F22" s="15"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="17" t="str">
         <f aca="false">IF(AND(F22&lt;&gt;"",G22&lt;&gt;""),F22*G22,"")</f>
         <v/>
       </c>
       <c r="I22" s="3"/>
-      <c r="J22" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A22,"00")</f>
-        <v>R-14</v>
-      </c>
-      <c r="K22" s="14" t="str">
+      <c r="J22" s="15"/>
+      <c r="K22" s="13" t="str">
         <f aca="false">"사진 "&amp;A22</f>
         <v>사진 14</v>
       </c>
-      <c r="L22" s="16"/>
+      <c r="L22" s="15"/>
       <c r="M22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="15"/>
+      <c r="B23" s="14"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="18" t="str">
+      <c r="F23" s="15"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="17" t="str">
         <f aca="false">IF(AND(F23&lt;&gt;"",G23&lt;&gt;""),F23*G23,"")</f>
         <v/>
       </c>
       <c r="I23" s="3"/>
-      <c r="J23" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A23,"00")</f>
-        <v>R-15</v>
-      </c>
-      <c r="K23" s="14" t="str">
+      <c r="J23" s="15"/>
+      <c r="K23" s="13" t="str">
         <f aca="false">"사진 "&amp;A23</f>
         <v>사진 15</v>
       </c>
-      <c r="L23" s="16"/>
+      <c r="L23" s="15"/>
       <c r="M23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="15"/>
+      <c r="B24" s="14"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="18" t="str">
+      <c r="F24" s="15"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="17" t="str">
         <f aca="false">IF(AND(F24&lt;&gt;"",G24&lt;&gt;""),F24*G24,"")</f>
         <v/>
       </c>
       <c r="I24" s="3"/>
-      <c r="J24" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A24,"00")</f>
-        <v>R-16</v>
-      </c>
-      <c r="K24" s="14" t="str">
+      <c r="J24" s="15"/>
+      <c r="K24" s="13" t="str">
         <f aca="false">"사진 "&amp;A24</f>
         <v>사진 16</v>
       </c>
-      <c r="L24" s="16"/>
+      <c r="L24" s="15"/>
       <c r="M24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="15"/>
+      <c r="B25" s="14"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="18" t="str">
+      <c r="F25" s="15"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="17" t="str">
         <f aca="false">IF(AND(F25&lt;&gt;"",G25&lt;&gt;""),F25*G25,"")</f>
         <v/>
       </c>
       <c r="I25" s="3"/>
-      <c r="J25" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A25,"00")</f>
-        <v>R-17</v>
-      </c>
-      <c r="K25" s="14" t="str">
+      <c r="J25" s="15"/>
+      <c r="K25" s="13" t="str">
         <f aca="false">"사진 "&amp;A25</f>
         <v>사진 17</v>
       </c>
-      <c r="L25" s="16"/>
+      <c r="L25" s="15"/>
       <c r="M25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="15"/>
+      <c r="B26" s="14"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="18" t="str">
+      <c r="F26" s="15"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="17" t="str">
         <f aca="false">IF(AND(F26&lt;&gt;"",G26&lt;&gt;""),F26*G26,"")</f>
         <v/>
       </c>
       <c r="I26" s="3"/>
-      <c r="J26" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A26,"00")</f>
-        <v>R-18</v>
-      </c>
-      <c r="K26" s="14" t="str">
+      <c r="J26" s="15"/>
+      <c r="K26" s="13" t="str">
         <f aca="false">"사진 "&amp;A26</f>
         <v>사진 18</v>
       </c>
-      <c r="L26" s="16"/>
+      <c r="L26" s="15"/>
       <c r="M26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="15"/>
+      <c r="B27" s="14"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="18" t="str">
+      <c r="F27" s="15"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="17" t="str">
         <f aca="false">IF(AND(F27&lt;&gt;"",G27&lt;&gt;""),F27*G27,"")</f>
         <v/>
       </c>
       <c r="I27" s="3"/>
-      <c r="J27" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A27,"00")</f>
-        <v>R-19</v>
-      </c>
-      <c r="K27" s="14" t="str">
+      <c r="J27" s="15"/>
+      <c r="K27" s="13" t="str">
         <f aca="false">"사진 "&amp;A27</f>
         <v>사진 19</v>
       </c>
-      <c r="L27" s="16"/>
+      <c r="L27" s="15"/>
       <c r="M27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B28" s="15"/>
+      <c r="B28" s="14"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="18" t="str">
+      <c r="F28" s="15"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="17" t="str">
         <f aca="false">IF(AND(F28&lt;&gt;"",G28&lt;&gt;""),F28*G28,"")</f>
         <v/>
       </c>
       <c r="I28" s="3"/>
-      <c r="J28" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A28,"00")</f>
-        <v>R-20</v>
-      </c>
-      <c r="K28" s="14" t="str">
+      <c r="J28" s="15"/>
+      <c r="K28" s="13" t="str">
         <f aca="false">"사진 "&amp;A28</f>
         <v>사진 20</v>
       </c>
-      <c r="L28" s="16"/>
+      <c r="L28" s="15"/>
       <c r="M28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="B29" s="15"/>
+      <c r="B29" s="14"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="18" t="str">
+      <c r="F29" s="15"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="17" t="str">
         <f aca="false">IF(AND(F29&lt;&gt;"",G29&lt;&gt;""),F29*G29,"")</f>
         <v/>
       </c>
       <c r="I29" s="3"/>
-      <c r="J29" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A29,"00")</f>
-        <v>R-21</v>
-      </c>
-      <c r="K29" s="14" t="str">
+      <c r="J29" s="15"/>
+      <c r="K29" s="13" t="str">
         <f aca="false">"사진 "&amp;A29</f>
         <v>사진 21</v>
       </c>
-      <c r="L29" s="16"/>
+      <c r="L29" s="15"/>
       <c r="M29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B30" s="15"/>
+      <c r="B30" s="14"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="18" t="str">
+      <c r="F30" s="15"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="17" t="str">
         <f aca="false">IF(AND(F30&lt;&gt;"",G30&lt;&gt;""),F30*G30,"")</f>
         <v/>
       </c>
       <c r="I30" s="3"/>
-      <c r="J30" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A30,"00")</f>
-        <v>R-22</v>
-      </c>
-      <c r="K30" s="14" t="str">
+      <c r="J30" s="15"/>
+      <c r="K30" s="13" t="str">
         <f aca="false">"사진 "&amp;A30</f>
         <v>사진 22</v>
       </c>
-      <c r="L30" s="16"/>
+      <c r="L30" s="15"/>
       <c r="M30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="B31" s="15"/>
+      <c r="B31" s="14"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="18" t="str">
+      <c r="F31" s="15"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="17" t="str">
         <f aca="false">IF(AND(F31&lt;&gt;"",G31&lt;&gt;""),F31*G31,"")</f>
         <v/>
       </c>
       <c r="I31" s="3"/>
-      <c r="J31" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A31,"00")</f>
-        <v>R-23</v>
-      </c>
-      <c r="K31" s="14" t="str">
+      <c r="J31" s="15"/>
+      <c r="K31" s="13" t="str">
         <f aca="false">"사진 "&amp;A31</f>
         <v>사진 23</v>
       </c>
-      <c r="L31" s="16"/>
+      <c r="L31" s="15"/>
       <c r="M31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B32" s="15"/>
+      <c r="B32" s="14"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="18" t="str">
+      <c r="F32" s="15"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="17" t="str">
         <f aca="false">IF(AND(F32&lt;&gt;"",G32&lt;&gt;""),F32*G32,"")</f>
         <v/>
       </c>
       <c r="I32" s="3"/>
-      <c r="J32" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A32,"00")</f>
-        <v>R-24</v>
-      </c>
-      <c r="K32" s="14" t="str">
+      <c r="J32" s="15"/>
+      <c r="K32" s="13" t="str">
         <f aca="false">"사진 "&amp;A32</f>
         <v>사진 24</v>
       </c>
-      <c r="L32" s="16"/>
+      <c r="L32" s="15"/>
       <c r="M32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="B33" s="15"/>
+      <c r="B33" s="14"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="18" t="str">
+      <c r="F33" s="15"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="17" t="str">
         <f aca="false">IF(AND(F33&lt;&gt;"",G33&lt;&gt;""),F33*G33,"")</f>
         <v/>
       </c>
       <c r="I33" s="3"/>
-      <c r="J33" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A33,"00")</f>
-        <v>R-25</v>
-      </c>
-      <c r="K33" s="14" t="str">
+      <c r="J33" s="15"/>
+      <c r="K33" s="13" t="str">
         <f aca="false">"사진 "&amp;A33</f>
         <v>사진 25</v>
       </c>
-      <c r="L33" s="16"/>
+      <c r="L33" s="15"/>
       <c r="M33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B34" s="15"/>
+      <c r="B34" s="14"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="18" t="str">
+      <c r="F34" s="15"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="17" t="str">
         <f aca="false">IF(AND(F34&lt;&gt;"",G34&lt;&gt;""),F34*G34,"")</f>
         <v/>
       </c>
       <c r="I34" s="3"/>
-      <c r="J34" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A34,"00")</f>
-        <v>R-26</v>
-      </c>
-      <c r="K34" s="14" t="str">
+      <c r="J34" s="15"/>
+      <c r="K34" s="13" t="str">
         <f aca="false">"사진 "&amp;A34</f>
         <v>사진 26</v>
       </c>
-      <c r="L34" s="16"/>
+      <c r="L34" s="15"/>
       <c r="M34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14" t="n">
+      <c r="A35" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="B35" s="15"/>
+      <c r="B35" s="14"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="18" t="str">
+      <c r="F35" s="15"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="17" t="str">
         <f aca="false">IF(AND(F35&lt;&gt;"",G35&lt;&gt;""),F35*G35,"")</f>
         <v/>
       </c>
       <c r="I35" s="3"/>
-      <c r="J35" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A35,"00")</f>
-        <v>R-27</v>
-      </c>
-      <c r="K35" s="14" t="str">
+      <c r="J35" s="15"/>
+      <c r="K35" s="13" t="str">
         <f aca="false">"사진 "&amp;A35</f>
         <v>사진 27</v>
       </c>
-      <c r="L35" s="16"/>
+      <c r="L35" s="15"/>
       <c r="M35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="n">
+      <c r="A36" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="B36" s="15"/>
+      <c r="B36" s="14"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="18" t="str">
+      <c r="F36" s="15"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="17" t="str">
         <f aca="false">IF(AND(F36&lt;&gt;"",G36&lt;&gt;""),F36*G36,"")</f>
         <v/>
       </c>
       <c r="I36" s="3"/>
-      <c r="J36" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A36,"00")</f>
-        <v>R-28</v>
-      </c>
-      <c r="K36" s="14" t="str">
+      <c r="J36" s="15"/>
+      <c r="K36" s="13" t="str">
         <f aca="false">"사진 "&amp;A36</f>
         <v>사진 28</v>
       </c>
-      <c r="L36" s="16"/>
+      <c r="L36" s="15"/>
       <c r="M36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="14" t="n">
+      <c r="A37" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="B37" s="15"/>
+      <c r="B37" s="14"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="18" t="str">
+      <c r="F37" s="15"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="17" t="str">
         <f aca="false">IF(AND(F37&lt;&gt;"",G37&lt;&gt;""),F37*G37,"")</f>
         <v/>
       </c>
       <c r="I37" s="3"/>
-      <c r="J37" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A37,"00")</f>
-        <v>R-29</v>
-      </c>
-      <c r="K37" s="14" t="str">
+      <c r="J37" s="15"/>
+      <c r="K37" s="13" t="str">
         <f aca="false">"사진 "&amp;A37</f>
         <v>사진 29</v>
       </c>
-      <c r="L37" s="16"/>
+      <c r="L37" s="15"/>
       <c r="M37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="14" t="n">
+      <c r="A38" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B38" s="15"/>
+      <c r="B38" s="14"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="18" t="str">
+      <c r="F38" s="15"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="17" t="str">
         <f aca="false">IF(AND(F38&lt;&gt;"",G38&lt;&gt;""),F38*G38,"")</f>
         <v/>
       </c>
       <c r="I38" s="3"/>
-      <c r="J38" s="14" t="str">
-        <f aca="false">"R-"&amp;TEXT(A38,"00")</f>
-        <v>R-30</v>
-      </c>
-      <c r="K38" s="14" t="str">
+      <c r="J38" s="15"/>
+      <c r="K38" s="13" t="str">
         <f aca="false">"사진 "&amp;A38</f>
         <v>사진 30</v>
       </c>
-      <c r="L38" s="16"/>
+      <c r="L38" s="15"/>
       <c r="M38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -3763,7 +4502,7 @@
       <c r="G39" s="2"/>
       <c r="H39" s="19" t="n">
         <f aca="false">SUM(H9:H38)</f>
-        <v>0</v>
+        <v>86240</v>
       </c>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
@@ -3813,7 +4552,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -3821,16 +4560,16 @@
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3840,10 +4579,10 @@
       </c>
       <c r="B3" s="22" t="str">
         <f aca="false">IF(정산보고서!D9="","",정산보고서!D9)</f>
-        <v/>
-      </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="15"/>
+        <v>말벌포획기 B형 (본체 + 유인액 2병)</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="n">
@@ -3852,10 +4591,10 @@
       </c>
       <c r="B4" s="22" t="str">
         <f aca="false">IF(정산보고서!D10="","",정산보고서!D10)</f>
-        <v/>
-      </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="15"/>
+        <v>배송비</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="n">
@@ -3864,10 +4603,10 @@
       </c>
       <c r="B5" s="22" t="str">
         <f aca="false">IF(정산보고서!D11="","",정산보고서!D11)</f>
-        <v/>
-      </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="15"/>
+        <v>라즈베리파이 27W USB-C 아답터 검은색 (공식 정품)</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="n">
@@ -3876,10 +4615,10 @@
       </c>
       <c r="B6" s="22" t="str">
         <f aca="false">IF(정산보고서!D12="","",정산보고서!D12)</f>
-        <v/>
-      </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="15"/>
+        <v>라즈베리파이5 액티브 쿨러 (정품)</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="n">
@@ -3888,10 +4627,10 @@
       </c>
       <c r="B7" s="22" t="str">
         <f aca="false">IF(정산보고서!D13="","",정산보고서!D13)</f>
-        <v/>
-      </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="15"/>
+        <v>배송비</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="n">
@@ -3902,8 +4641,8 @@
         <f aca="false">IF(정산보고서!D14="","",정산보고서!D14)</f>
         <v/>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="n">
@@ -3914,8 +4653,8 @@
         <f aca="false">IF(정산보고서!D15="","",정산보고서!D15)</f>
         <v/>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="n">
@@ -3926,8 +4665,8 @@
         <f aca="false">IF(정산보고서!D16="","",정산보고서!D16)</f>
         <v/>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="n">
@@ -3938,8 +4677,8 @@
         <f aca="false">IF(정산보고서!D17="","",정산보고서!D17)</f>
         <v/>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="n">
@@ -3950,8 +4689,8 @@
         <f aca="false">IF(정산보고서!D18="","",정산보고서!D18)</f>
         <v/>
       </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="n">
@@ -3962,8 +4701,8 @@
         <f aca="false">IF(정산보고서!D19="","",정산보고서!D19)</f>
         <v/>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="n">
@@ -3974,8 +4713,8 @@
         <f aca="false">IF(정산보고서!D20="","",정산보고서!D20)</f>
         <v/>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="14"/>
     </row>
     <row r="15" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="n">
@@ -3986,8 +4725,8 @@
         <f aca="false">IF(정산보고서!D21="","",정산보고서!D21)</f>
         <v/>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="14"/>
     </row>
     <row r="16" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="n">
@@ -3998,8 +4737,8 @@
         <f aca="false">IF(정산보고서!D22="","",정산보고서!D22)</f>
         <v/>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="14"/>
     </row>
     <row r="17" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="n">
@@ -4010,8 +4749,8 @@
         <f aca="false">IF(정산보고서!D23="","",정산보고서!D23)</f>
         <v/>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="n">
@@ -4022,8 +4761,8 @@
         <f aca="false">IF(정산보고서!D24="","",정산보고서!D24)</f>
         <v/>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="n">
@@ -4034,8 +4773,8 @@
         <f aca="false">IF(정산보고서!D25="","",정산보고서!D25)</f>
         <v/>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="n">
@@ -4046,8 +4785,8 @@
         <f aca="false">IF(정산보고서!D26="","",정산보고서!D26)</f>
         <v/>
       </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="n">
@@ -4058,8 +4797,8 @@
         <f aca="false">IF(정산보고서!D27="","",정산보고서!D27)</f>
         <v/>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="n">
@@ -4070,8 +4809,8 @@
         <f aca="false">IF(정산보고서!D28="","",정산보고서!D28)</f>
         <v/>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="n">
@@ -4082,8 +4821,8 @@
         <f aca="false">IF(정산보고서!D29="","",정산보고서!D29)</f>
         <v/>
       </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="n">
@@ -4094,8 +4833,8 @@
         <f aca="false">IF(정산보고서!D30="","",정산보고서!D30)</f>
         <v/>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="14"/>
     </row>
     <row r="25" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="n">
@@ -4106,8 +4845,8 @@
         <f aca="false">IF(정산보고서!D31="","",정산보고서!D31)</f>
         <v/>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="14"/>
     </row>
     <row r="26" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="n">
@@ -4118,8 +4857,8 @@
         <f aca="false">IF(정산보고서!D32="","",정산보고서!D32)</f>
         <v/>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="14"/>
     </row>
     <row r="27" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="n">
@@ -4130,8 +4869,8 @@
         <f aca="false">IF(정산보고서!D33="","",정산보고서!D33)</f>
         <v/>
       </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="n">
@@ -4142,8 +4881,8 @@
         <f aca="false">IF(정산보고서!D34="","",정산보고서!D34)</f>
         <v/>
       </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="14"/>
     </row>
     <row r="29" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="n">
@@ -4154,8 +4893,8 @@
         <f aca="false">IF(정산보고서!D35="","",정산보고서!D35)</f>
         <v/>
       </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="14"/>
     </row>
     <row r="30" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="n">
@@ -4166,8 +4905,8 @@
         <f aca="false">IF(정산보고서!D36="","",정산보고서!D36)</f>
         <v/>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="14"/>
     </row>
     <row r="31" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="n">
@@ -4178,8 +4917,8 @@
         <f aca="false">IF(정산보고서!D37="","",정산보고서!D37)</f>
         <v/>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="14"/>
     </row>
     <row r="32" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="n">
@@ -4190,8 +4929,8 @@
         <f aca="false">IF(정산보고서!D38="","",정산보고서!D38)</f>
         <v/>
       </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4221,77 +4960,77 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="23" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="24" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="24" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="24" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="24" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="23" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="24" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="23" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="24" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="23" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="24" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="23" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="24" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/purchase/재료비_정산보고서.xlsx
+++ b/purchase/재료비_정산보고서.xlsx
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="93">
   <si>
     <r>
       <rPr>
@@ -293,25 +293,7 @@
     <t xml:space="preserve">레트로핏 모듈의 바탕 상용 트랩 — 포획통을 격리함으로 사용, 설계 실측·표본 채집</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">영수증</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
+    <t xml:space="preserve">영수증1</t>
   </si>
   <si>
     <t xml:space="preserve">배송비</t>
@@ -356,25 +338,7 @@
     <t xml:space="preserve">제어부 190 — Pi 5 + AI HAT+ + 카메라 전원</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">영수증</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
+    <t xml:space="preserve">영수증2</t>
   </si>
   <si>
     <t xml:space="preserve">영수증에 "외 1건"으로만 표시 → 주문 상세 캡처를 세부내역으로 첨부</t>
@@ -422,31 +386,43 @@
     <t xml:space="preserve">설계 실측(흉부 폭·몸 높이), 마킹·검출 시험(J4·J8), VespAI 재학습 사진</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">영수증</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
+    <t xml:space="preserve">영수증3</t>
   </si>
   <si>
     <t xml:space="preserve">표본이 "재료"로 인정되는지 확인 필요. 상품 주문 21,000원(7개)</t>
   </si>
   <si>
     <t xml:space="preserve">하멜른</t>
+  </si>
+  <si>
+    <t xml:space="preserve">월드크린 테프론 테이프 4m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTFE 테이프, 4 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마커 잉크 부착 시험(J9) 시편 — 말벌 몸 표면처럼 잘 안 붙는 표면 대용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">영수증5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">영수증5 = 거래명세표(PDF) + 카드영수증(캡처, 카드번호 일부 보임 → 레포 X)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">샤피 크리에이티브 수성 마커 총알팁 12색</t>
+  </si>
+  <si>
+    <t xml:space="preserve">수성 아크릴, 불렛(총알) 팁, 12색 1세트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마커 201 — 말벌 흉부 표식 잉크 (노랑 사용), 점 크기·건조 시험(J9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">영수증6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">영수증6은 개인 물품 3개와 함께 주문 — 이 품목만 청구(1행). 주문 할인 2,900원이 어느 상품에 붙었는지 확인 필요: 이 상품이면 금액 줄임 (안분 시 17,761원)</t>
   </si>
   <si>
     <t xml:space="preserve">합계</t>
@@ -827,7 +803,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1175,7 +1151,7 @@
         <v>9</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1191,14 +1167,14 @@
       </c>
       <c r="E4" s="7" t="n">
         <f aca="false">SUM(H9:H38)</f>
-        <v>110240</v>
+        <v>130010</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="7" t="n">
         <f aca="false">C4-E4</f>
-        <v>389760</v>
+        <v>369990</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>13</v>
@@ -1615,47 +1591,87 @@
       <c r="A16" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="18" t="str">
+      <c r="B16" s="15" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>900</v>
+      </c>
+      <c r="H16" s="18" t="n">
         <f aca="false">IF(AND(F16&lt;&gt;"",G16&lt;&gt;""),F16*G16,"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="4"/>
-      <c r="J16" s="16"/>
+        <v>900</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>67</v>
+      </c>
       <c r="K16" s="14" t="str">
         <f aca="false">"사진 "&amp;A16</f>
         <v>사진 8</v>
       </c>
-      <c r="L16" s="16"/>
-      <c r="M16" s="4"/>
+      <c r="L16" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="18" t="str">
+      <c r="B17" s="15" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>18870</v>
+      </c>
+      <c r="H17" s="18" t="n">
         <f aca="false">IF(AND(F17&lt;&gt;"",G17&lt;&gt;""),F17*G17,"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="16"/>
+        <v>18870</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>72</v>
+      </c>
       <c r="K17" s="14" t="str">
         <f aca="false">"사진 "&amp;A17</f>
         <v>사진 9</v>
       </c>
-      <c r="L17" s="16"/>
-      <c r="M17" s="4"/>
+      <c r="L17" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="n">
@@ -2142,7 +2158,7 @@
     </row>
     <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2152,7 +2168,7 @@
       <c r="G39" s="3"/>
       <c r="H39" s="21" t="n">
         <f aca="false">SUM(H9:H38)</f>
-        <v>110240</v>
+        <v>130010</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
@@ -2202,7 +2218,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="22" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -2216,10 +2232,10 @@
         <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2313,7 +2329,7 @@
       </c>
       <c r="B10" s="24" t="str">
         <f aca="false">IF(정산보고서!D16="","",정산보고서!D16)</f>
-        <v/>
+        <v>월드크린 테프론 테이프 4m</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="15"/>
@@ -2325,7 +2341,7 @@
       </c>
       <c r="B11" s="24" t="str">
         <f aca="false">IF(정산보고서!D17="","",정산보고서!D17)</f>
-        <v/>
+        <v>샤피 크리에이티브 수성 마커 총알팁 12색</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="15"/>
@@ -2610,77 +2626,77 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="25" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="26" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="26" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="26" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="26" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="25" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="26" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="25" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="26" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="26" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="25" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="26" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="26" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="25" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="26" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/purchase/재료비_정산보고서.xlsx
+++ b/purchase/재료비_정산보고서.xlsx
@@ -422,7 +422,7 @@
     <t xml:space="preserve">영수증6</t>
   </si>
   <si>
-    <t xml:space="preserve">영수증6은 개인 물품 3개와 함께 주문 — 이 품목만 청구(1행). 주문 할인 2,900원이 어느 상품에 붙었는지 확인 필요: 이 상품이면 금액 줄임 (안분 시 17,761원)</t>
+    <t xml:space="preserve">영수증6은 개인 물품 3개와 함께 주문 — 이 품목만 청구(1행). 주문 할인 2,900원은 여러 개 같이 사서 붙은 할인 → 샤피는 18,870원으로 청구 (승준 판단 10/29)</t>
   </si>
   <si>
     <t xml:space="preserve">합계</t>
